--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2020_T4_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2020_T4_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>76</t>
+    <t>70</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>1.440</t>
-  </si>
-  <si>
-    <t>(0.232)</t>
-  </si>
-  <si>
-    <t>7.947</t>
-  </si>
-  <si>
-    <t>(0.947)</t>
-  </si>
-  <si>
-    <t>3.324</t>
-  </si>
-  <si>
-    <t>(1.161)</t>
-  </si>
-  <si>
-    <t>19.504</t>
-  </si>
-  <si>
-    <t>(8.834)</t>
-  </si>
-  <si>
-    <t>10.576</t>
-  </si>
-  <si>
-    <t>(8.751)</t>
-  </si>
-  <si>
-    <t>9.921</t>
-  </si>
-  <si>
-    <t>(1.030)</t>
-  </si>
-  <si>
-    <t>2.580</t>
-  </si>
-  <si>
-    <t>(0.471)</t>
-  </si>
-  <si>
-    <t>1.585</t>
-  </si>
-  <si>
-    <t>(0.519)</t>
-  </si>
-  <si>
-    <t>33.507</t>
-  </si>
-  <si>
-    <t>(20.149)</t>
-  </si>
-  <si>
-    <t>8.549</t>
-  </si>
-  <si>
-    <t>(2.470)</t>
+    <t>1.389</t>
+  </si>
+  <si>
+    <t>(0.194)</t>
+  </si>
+  <si>
+    <t>8.614</t>
+  </si>
+  <si>
+    <t>(0.988)</t>
+  </si>
+  <si>
+    <t>2.394</t>
+  </si>
+  <si>
+    <t>(0.428)</t>
+  </si>
+  <si>
+    <t>8.602</t>
+  </si>
+  <si>
+    <t>(0.985)</t>
+  </si>
+  <si>
+    <t>1.711</t>
+  </si>
+  <si>
+    <t>(0.184)</t>
+  </si>
+  <si>
+    <t>10.586</t>
+  </si>
+  <si>
+    <t>(1.074)</t>
+  </si>
+  <si>
+    <t>2.305</t>
+  </si>
+  <si>
+    <t>(0.381)</t>
+  </si>
+  <si>
+    <t>0.803</t>
+  </si>
+  <si>
+    <t>(0.297)</t>
+  </si>
+  <si>
+    <t>10.942</t>
+  </si>
+  <si>
+    <t>(1.229)</t>
+  </si>
+  <si>
+    <t>6.340</t>
+  </si>
+  <si>
+    <t>(0.847)</t>
   </si>
   <si>
     <t>40</t>
@@ -198,7 +198,7 @@
     <t>(2.329)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.044</t>
-  </si>
-  <si>
-    <t>1.978</t>
-  </si>
-  <si>
-    <t>1.139</t>
-  </si>
-  <si>
-    <t>-8.221</t>
-  </si>
-  <si>
-    <t>-9.079</t>
-  </si>
-  <si>
-    <t>-0.346</t>
-  </si>
-  <si>
-    <t>0.943</t>
-  </si>
-  <si>
-    <t>-1.268*</t>
-  </si>
-  <si>
-    <t>-20.537</t>
-  </si>
-  <si>
-    <t>1.728</t>
+    <t>0.094</t>
+  </si>
+  <si>
+    <t>1.311</t>
+  </si>
+  <si>
+    <t>2.070**</t>
+  </si>
+  <si>
+    <t>2.681</t>
+  </si>
+  <si>
+    <t>-0.214</t>
+  </si>
+  <si>
+    <t>-1.011</t>
+  </si>
+  <si>
+    <t>1.218</t>
+  </si>
+  <si>
+    <t>-0.486</t>
+  </si>
+  <si>
+    <t>2.028</t>
+  </si>
+  <si>
+    <t>3.938*</t>
   </si>
 </sst>
 </file>
